--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260831.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260831.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>4.09%</t>
         </is>
       </c>
     </row>
@@ -633,78 +633,78 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>10,306,000</t>
+          <t>10,424,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.81%</t>
+          <t>3.82%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>4,570,402,944</t>
+          <t>21,637,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>21,637,000</t>
+          <t>6,066,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>6,066,000</t>
+          <t>48,740,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -726,29 +726,29 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>47,925,000</t>
+          <t>543,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -787,34 +787,34 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3,875,000</t>
+          <t>3,919,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>543,000</t>
+          <t>3,891,663,036</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>11,265,000</t>
+          <t>11,407,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>20,426,000</t>
+          <t>20,627,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -902,29 +902,29 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>6,624,000</t>
+          <t>22,764,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
@@ -946,29 +946,29 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>36,304,000</t>
+          <t>6,739,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -990,73 +990,73 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>22,764,000</t>
+          <t>36,304,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>32,953,000</t>
+          <t>4,345,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>4,161,000</t>
+          <t>32,953,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,187,000</t>
+          <t>2,217,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,845,000</t>
+          <t>2,883,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -1166,29 +1166,29 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,213,000</t>
+          <t>41,037,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -1210,29 +1210,29 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>41,037,000</t>
+          <t>15,213,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,675,121,747</t>
+          <t>2,644,721,747</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>7,883,000</t>
+          <t>6,179,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,22 +1305,22 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>6,179,000</t>
+          <t>4,984,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -1342,156 +1342,156 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>4,984,000</t>
+          <t>7,883,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>14,405,000</t>
+          <t>24,954,004</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,901,000</t>
+          <t>14,405,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>24,954,004</t>
+          <t>3,901,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>9,936,000</t>
+          <t>16,642,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>16,642,000</t>
+          <t>10,241,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>15,340,000</t>
+          <t>9,303,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,22 +1503,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>8,984,000</t>
+          <t>15,340,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1628,51 +1628,51 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>18,852,000</t>
+          <t>48,160,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>48,160,000</t>
+          <t>18,852,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
